--- a/outputs/step_disease_logistic/ckd/ckd_logistic_coefficients.xlsx
+++ b/outputs/step_disease_logistic/ckd/ckd_logistic_coefficients.xlsx
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.7085</v>
+        <v>1.1503</v>
       </c>
       <c r="C2" t="n">
-        <v>5.5209</v>
+        <v>3.159</v>
       </c>
     </row>
     <row r="3">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7124</v>
+        <v>0.7064</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0388</v>
+        <v>2.0268</v>
       </c>
     </row>
     <row r="4">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2258</v>
+        <v>-0.3151</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.7297</v>
       </c>
     </row>
     <row r="5">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1347</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1442</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="6">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-3.6439</v>
+        <v>-3.3192</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0262</v>
+        <v>0.0362</v>
       </c>
     </row>
   </sheetData>
@@ -552,10 +552,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.7894</v>
+        <v>1.1576</v>
       </c>
       <c r="C2" t="n">
-        <v>5.9857</v>
+        <v>3.1822</v>
       </c>
     </row>
     <row r="3">
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6676</v>
+        <v>0.6974</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9495</v>
+        <v>2.0084</v>
       </c>
     </row>
     <row r="4">
@@ -578,10 +578,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1905</v>
+        <v>-0.2991</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8266</v>
+        <v>0.7415</v>
       </c>
     </row>
     <row r="5">
@@ -591,10 +591,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0716</v>
+        <v>0.4803</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9308999999999999</v>
+        <v>1.6166</v>
       </c>
     </row>
     <row r="6">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3182</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3746</v>
+        <v>1.0777</v>
       </c>
     </row>
     <row r="7">
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-3.6986</v>
+        <v>-3.3222</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0248</v>
+        <v>0.0361</v>
       </c>
     </row>
   </sheetData>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.4332</v>
+        <v>0.8257</v>
       </c>
       <c r="C2" t="n">
-        <v>4.1919</v>
+        <v>2.2835</v>
       </c>
     </row>
     <row r="3">
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5596</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7499</v>
+        <v>1.9187</v>
       </c>
     </row>
     <row r="4">
@@ -687,10 +687,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.2531</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9163</v>
+        <v>0.7764</v>
       </c>
     </row>
     <row r="5">
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2192</v>
+        <v>0.387</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8032</v>
+        <v>1.4726</v>
       </c>
     </row>
     <row r="6">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2054</v>
+        <v>0.0521</v>
       </c>
       <c r="C6" t="n">
-        <v>1.228</v>
+        <v>1.0535</v>
       </c>
     </row>
     <row r="7">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1753</v>
+        <v>0.0646</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1916</v>
+        <v>1.0668</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.4993</v>
+        <v>-0.3545</v>
       </c>
       <c r="C8" t="n">
-        <v>0.607</v>
+        <v>0.7015</v>
       </c>
     </row>
     <row r="9">
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0013</v>
+        <v>-0.1019</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0013</v>
+        <v>0.9032</v>
       </c>
     </row>
     <row r="10">
@@ -765,10 +765,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-3.6622</v>
+        <v>-3.2471</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0257</v>
+        <v>0.0389</v>
       </c>
     </row>
   </sheetData>
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.2556</v>
+        <v>1.2955</v>
       </c>
       <c r="C2" t="n">
-        <v>9.541</v>
+        <v>3.6528</v>
       </c>
     </row>
     <row r="3">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6864</v>
+        <v>0.6566</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9866</v>
+        <v>1.9283</v>
       </c>
     </row>
     <row r="4">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0537</v>
+        <v>-0.263</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9477</v>
+        <v>0.7688</v>
       </c>
     </row>
     <row r="5">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.327</v>
+        <v>0.3237</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7211</v>
+        <v>1.3822</v>
       </c>
     </row>
     <row r="6">
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.1458</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0983</v>
+        <v>1.1569</v>
       </c>
     </row>
     <row r="7">
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5302</v>
+        <v>0.1485</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6993</v>
+        <v>1.1601</v>
       </c>
     </row>
     <row r="8">
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-3.882</v>
+        <v>-3.3791</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0206</v>
+        <v>0.0341</v>
       </c>
     </row>
   </sheetData>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.9899</v>
+        <v>1.0513</v>
       </c>
       <c r="C2" t="n">
-        <v>7.3149</v>
+        <v>2.8614</v>
       </c>
     </row>
     <row r="3">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6432</v>
+        <v>0.6617</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9025</v>
+        <v>1.938</v>
       </c>
     </row>
     <row r="4">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0235</v>
+        <v>-0.2235</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0238</v>
+        <v>0.7997</v>
       </c>
     </row>
     <row r="5">
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.466</v>
+        <v>0.2557</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6274999999999999</v>
+        <v>1.2914</v>
       </c>
     </row>
     <row r="6">
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1055</v>
+        <v>0.0569</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8999</v>
+        <v>1.0585</v>
       </c>
     </row>
     <row r="7">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5766</v>
+        <v>0.2231</v>
       </c>
       <c r="C7" t="n">
-        <v>1.78</v>
+        <v>1.2499</v>
       </c>
     </row>
     <row r="8">
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2683</v>
+        <v>0.0541</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3077</v>
+        <v>1.0555</v>
       </c>
     </row>
     <row r="9">
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.5103</v>
+        <v>-0.3303</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.7187</v>
       </c>
     </row>
     <row r="10">
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0853</v>
+        <v>-0.1546</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0891</v>
+        <v>0.8567</v>
       </c>
     </row>
     <row r="11">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-3.9031</v>
+        <v>-3.3426</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0202</v>
+        <v>0.0353</v>
       </c>
     </row>
   </sheetData>
